--- a/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
+++ b/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Q2 gate. LOW = mics + Rec LED on. 100k pull-up to 3V3.</t>
+          <t>Q2 gate. LOW = mics + Rec LED on. 100k pull-up to +3V3.</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>3V3</t>
+          <t>+3V3</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>3V3</t>
+          <t>+3V3</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -1496,7 +1496,7 @@
       <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Fuel gauge, accel, haptic driver. 4.7k pull-up to 3V3.</t>
+          <t>Fuel gauge, accel, haptic driver. 4.7k pull-up to +3V3.</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Same bus. 4.7k pull-up to 3V3.</t>
+          <t>Same bus. 4.7k pull-up to +3V3.</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Use this when drawing the schematic: one row per net. Device pins are listed by name; check pin numbers in each footprint.</t>
+          <t>Use this when drawing the schematic: one row per net. Device pins are listed by name; check pin numbers in each footprint. Net names match the KiCad power symbols (+BATT, +3V3, VBUS, GND).</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>VBAT</t>
+          <t>+BATT</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>USB_VBUS</t>
+          <t>VBUS</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>R14 (2.2R from USB_VBUS), U1 VBUS (32), 10 uF to GND</t>
+          <t>R14 (2.2R from VBUS), U1 VBUS (32), 10 uF to GND</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>3V3</t>
+          <t>+3V3</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.13, U6 SDA, U7 SDA, U8 SDA, R3 (to 3V3)</t>
+          <t>U1 P0.13, U6 SDA, U7 SDA, U8 SDA, R3 (to +3V3)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.14, U6 SCL, U7 SCL, U8 SCL, R4 (to 3V3)</t>
+          <t>U1 P0.14, U6 SCL, U7 SCL, U8 SCL, R4 (to +3V3)</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>U1 P1.15, Q2 gate, R13 (to 3V3)</t>
+          <t>U1 P1.15, Q2 gate, R13 (to +3V3)</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>D3 anode via R11 to USB_VBUS.</t>
+          <t>D3 anode via R11 to VBUS.</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Plus GND and 3V3 pads.</t>
+          <t>Plus GND and +3V3 pads.</t>
         </is>
       </c>
     </row>

--- a/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
+++ b/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
@@ -2274,7 +2274,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>U9 OUT, U1 VDD (28) + VDDH (30), U4 VCC, U7 VDD + VDDIO + CS, Q2 source, R3, R4, R13</t>
+          <t>U9 OUT, U1 VDD (28) + VDDH (30), U4 VCC, U7 VDD + VDDIO + CS + SDO/SA0, Q2 source, R3, R4, R13</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>All GND pins, J1 CC resistors, U2 SELECT, U5 VSS, U6 CTG + QSTRT, U7 SDO/SA0, U8 IN/TRIG, SW1, D1/D2 cathodes, R5, R6, R12</t>
+          <t>All GND pins, J1 CC resistors, U2 SELECT, U5 VSS, U6 CTG + QSTRT, U7 GND + RES, U8 IN/TRIG, SW1, D1/D2 cathodes, R5, R6, R12</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Addresses: LIS2DW12 0x18 (SA0 low), MAX17048 0x36, DRV2605L 0x5A - no conflicts.</t>
+          <t>Addresses: LIS2DW12 0x19 (SA0 high; its internal pull-up cannot be disabled), MAX17048 0x36, DRV2605L 0x5A - no conflicts.</t>
         </is>
       </c>
     </row>

--- a/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
+++ b/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
@@ -1218,7 +1218,7 @@
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>RGB blue via 100R. PWM, high drive. HIGH = on.</t>
+          <t>Gate of Q5 (blue cathode switch), R17 100k pull-down. PWM. HIGH = on.</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>RGB red via 1k. PWM. HIGH = on.</t>
+          <t>Gate of Q3 (red cathode switch), R15 100k pull-down. PWM. HIGH = on.</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>RGB green via 100R. PWM, high drive. HIGH = on.</t>
+          <t>Gate of Q4 (green cathode switch), R16 100k pull-down. PWM. HIGH = on.</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>J2 (+), U5 OUT, U9 IN + EN, U6 CELL + VDD, U8 VDD, BZ1 (+), D4 cathode</t>
+          <t>J2 (+), U5 OUT, U9 IN + EN, U6 CELL + VDD, U8 VDD, BZ1 (+), D4 cathode, D2 common anode (pin 1)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>All GND pins, J1 CC resistors, U2 SELECT, U5 VSS, U6 CTG + QSTRT, U7 GND + RES, U8 IN/TRIG, SW1, D1/D2 cathodes, R5, R6, R12</t>
+          <t>All GND pins, J1 CC resistors, U2 SELECT, U5 VSS, U6 CTG + QSTRT, U7 GND + RES, U8 IN/TRIG, SW1, D1 cathode, Q1/Q3/Q4/Q5 sources, R5, R6, R12, R15, R16, R17</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.11 / P0.12 / P1.08 -&gt; R8 1k / R9 100R / R10 100R -&gt; D2 anodes</t>
+          <t>U1 P0.11 / P0.12 / P1.08 -&gt; Q3 / Q4 / Q5 gates (R15 / R16 / R17 100k to GND). Q3 / Q4 / Q5 drains -&gt; R8 1k / R9 560R / R10 560R -&gt; D2 R (4) / G (3) / B (2) cathodes</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>D2 common cathode to GND.</t>
+          <t>D2 common anode (pin 1) on +BATT. About 2 mA per colour at 3.7 V. HIGH = on. JOT-HW-001 draft 3.</t>
         </is>
       </c>
     </row>

--- a/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
+++ b/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>J2 (+), U5 OUT, U9 IN + EN, U6 CELL + VDD, U8 VDD, BZ1 (+), D4 cathode, D2 common anode (pin 1)</t>
+          <t>J2 (+), U5 OUT, U9 IN + EN, U6 CELL + VDD, U8 VDD, R19 10R (to BZ1 (+) and D4 cathode), D2 common anode (pin 1)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>U9 OUT, U1 VDD (28) + VDDH (30), U4 VCC, U7 VDD + VDDIO + CS + SDO/SA0, Q2 source, R3, R4, R13</t>
+          <t>U9 OUT, U1 VDD (28) + VDDH (30), U4 VCC, U7 VDD + VDDIO + CS + SDO/SA0, Q2 source, R3, R4, R13, R18</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -2402,10 +2402,14 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.17, U4 /CS</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
+          <t>U1 P0.17, U4 /CS, R18 100k to +3V3</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Pull-up keeps the flash deselected during power-up and reset (W25Q01JV: /CS must track VCC).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">

--- a/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
+++ b/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
@@ -2208,7 +2208,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>J2 (+), U5 OUT, U9 IN + EN, U6 CELL + VDD, U8 VDD, R19 10R (to BZ1 (+) and D4 cathode), D2 common anode (pin 1)</t>
+          <t>J2 (+), U5 VBAT (3), U9 IN + EN, U6 CELL + VDD, U8 VDD, R19 10R (to BZ1 (+) and D4 cathode), D2 common anode (pin 1)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>J1 VBUS, U10 VBUS, U5 IN, R14, R11 -&gt; D3 anode</t>
+          <t>J1 VBUS, U10 VBUS, U5 VDD (4), C1 4.7 uF, R14, R11 -&gt; D3 anode</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>All GND pins, J1 CC resistors, U2 SELECT, U5 VSS, U6 CTG + QSTRT, U7 GND + RES, U8 IN/TRIG, SW1, D1 cathode, Q1/Q3/Q4/Q5 sources, R5, R6, R12, R15, R16, R17</t>
+          <t>All GND pins, J1 CC resistors, U2 SELECT, U5 VSS, U6 CTG + QSTRT, U7 GND + RES, U8 IN/TRIG, SW1, D1 cathode, Q1/Q3/Q4/Q5 sources, R6, R12, R15, R16, R17</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2717,17 +2717,17 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>CHG</t>
+          <t>STAT</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>U5 CHG, D3 cathode</t>
+          <t>U5 STAT (1), D3 cathode</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>D3 anode via R11 to VBUS.</t>
+          <t>D3 anode via R11 2.2k to VBUS. STAT low = charging (LED on), high = complete (off), Hi-Z = no input.</t>
         </is>
       </c>
     </row>
@@ -2739,15 +2739,19 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>ISET / TS</t>
+          <t>PROG</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>U5 ISET -&gt; R6 680R -&gt; GND; U5 TS -&gt; R5 10k -&gt; GND</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr"/>
+          <t>U5 PROG (5) -&gt; R6 5.1k -&gt; GND</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Charge current = 1000 V / 5.1k = 196 mA (MCP73831). No TS pin.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">

--- a/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
+++ b/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Side button to GND. Internal pull-up. Wakes from System OFF.</t>
+          <t>Side button to GND via R5 1k series resistor (ESD). Internal pull-up. Wakes from System OFF.</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>(spare)</t>
+          <t>CHG_INHIBIT</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>Slow</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -666,7 +666,11 @@
           <t>Low-freq only</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Q8 gate (R21 100k pull-down). HIGH = charging off (Q8 pulls Q7 gate low, PROG floats). LOW or MCU off/reset = charging on. Firmware: HIGH outside ~5-40 C while USB is present.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1014,7 +1018,7 @@
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>32.768 kHz crystal + load cap.</t>
+          <t>Y1 pin 2 + C8 18 pF to GND.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1044,7 @@
       <c r="E22" s="8" t="inlineStr"/>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>32.768 kHz crystal + load cap.</t>
+          <t>Y1 pin 1 + C9 18 pF to GND.</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1500,7 @@
       <c r="E40" s="7" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Fuel gauge, accel, haptic driver. 4.7k pull-up to +3V3.</t>
+          <t>Fuel gauge, accel, haptic driver. 2.2k pull-up to +3V3 (R4).</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1526,7 @@
       <c r="E41" s="7" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Same bus. 4.7k pull-up to +3V3.</t>
+          <t>Same bus. 2.2k pull-up to +3V3 (R3).</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1800,7 @@
       <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Q1 gate, ~4 kHz PWM. 100k pull-down.</t>
+          <t>Q1 gate, ~4 kHz PWM. 100k pull-down. Drive only from the PWM peripheral: never hold HIGH (R19 1 W limits a stuck-on fault).</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2208,12 +2212,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>J2 (+), U5 VBAT (3), U9 IN + EN, U6 CELL + VDD, U8 VDD, R19 10R (to BZ1 (+) and D4 cathode), D2 common anode (pin 1)</t>
+          <t>Q6 source (battery side via F1/Q6 from J2), U5 VBAT (3), U9 IN + EN, U6 CELL + VDD, U8 VDD, R19 10R 1 W (to BZ1 (+) and D4 cathode), D2 common anode (pin 1)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Battery rail, 3.0-4.2 V.</t>
+          <t>Battery rail, 3.0-4.2 V. J2 pin 1 -&gt; BATT_RAW -&gt; F1 polyfuse (0.5 A hold / 1 A trip) -&gt; BATT_FUSED -&gt; Q6 AO3401A (drain) -&gt; (source) +BATT; Q6 gate to GND (reverse-battery protection).</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2234,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>J1 VBUS, U10 VBUS, U5 VDD (4), C1 4.7 uF, R14, R11 -&gt; D3 anode</t>
+          <t>J1 VBUS, D5 SMF5.0A cathode (TVS, anode GND), U10 VBUS, U5 VDD (4), C1 4.7 uF, R14, R11 -&gt; D3 anode, R20 100k (to Q7 gate)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>USB 5 V.</t>
+          <t>USB 5 V. D5 next to J1.</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2278,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>U9 OUT, U1 VDD (28) + VDDH (30), U4 VCC, U7 VDD + VDDIO + CS + SDO/SA0, Q2 source, R3, R4, R13, R18</t>
+          <t>U9 OUT, U1 VDD (28) + VDDH (30), U4 VCC, U7 VDD + VDDIO + CS + SDO/SA0, Q2 source, R3, R4, R13, R18, TP6 (sense only: do not supply power here)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -2345,7 +2349,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Solid ground pour.</t>
+          <t>Solid ground pour. Also Q6 gate, Q7/Q8 sources, R21, D5 anode.</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2411,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Pull-up keeps the flash deselected during power-up and reset (W25Q01JV: /CS must track VCC).</t>
+          <t>Pull-up keeps the flash deselected during power-up and reset (/CS must track VCC). Flash W25Q256JVEIQ (32 MB).</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2518,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.13, U6 SDA, U7 SDA, U8 SDA, R3 (to +3V3)</t>
+          <t>U1 P0.13, U6 SDA, U7 SDA, U8 SDA, R3 2.2k (to +3V3)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -2536,10 +2540,14 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.14, U6 SCL, U7 SCL, U8 SCL, R4 (to +3V3)</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
+          <t>U1 P0.14, U6 SCL, U7 SCL, U8 SCL, R4 2.2k (to +3V3)</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>2.2k: MAX17048 allows 60 pF input capacitance and a 300 ns max rise time.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2634,12 +2642,12 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>U1 P1.10, SW1</t>
+          <t>U1 P1.10, R5 1k -&gt; SW1</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>SW1 other side to GND.</t>
+          <t>SW1 other side to GND. R5 near U1 (ESD).</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2752,12 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>U5 PROG (5) -&gt; R6 5.1k -&gt; GND</t>
+          <t>U5 PROG (5) -&gt; R6 5.1k -&gt; Q7 drain; Q7 source GND</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Charge current = 1000 V / 5.1k = 196 mA (MCP73831). No TS pin.</t>
+          <t>Charge current = 1000 V / 5.1k = 196 mA (MCP73831). Q7 off = PROG floats = charging disabled (datasheet 3.5, 4.3).</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2832,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.00 / P0.01, Y1, load caps to GND</t>
+          <t>U1 P0.00 / P0.01, Y1 pins 2 / 1, C8 / C9 18 pF to GND</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
@@ -2890,6 +2898,50 @@
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Charger</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CHG_INHIBIT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>U1 P1.11 (4), Q8 gate, R21 100k to GND</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HIGH = charging off. Default (MCU off/reset) = on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Charger</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Q7 gate</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>R20 100k to VBUS, Q7 gate, Q8 drain</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pulled to VBUS: charging allowed whenever USB is present unless Q8 is on.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
+++ b/Schematics/RevA/BOM/Jot_RevA_Pin_List.xlsx
@@ -535,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1210,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>LED_B</t>
+          <t>LED_R</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -1222,7 +1221,7 @@
       <c r="E29" s="7" t="n"/>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Gate of Q5 (blue cathode switch), R17 100k pull-down. PWM. HIGH = on.</t>
+          <t>Gate of Q3 (red cathode switch), R15 100k pull-down. PWM. HIGH = on. (Was LED_B before 16 Oct.)</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1258,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>LED_R</t>
+          <t>LED_G</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1270,7 +1269,7 @@
       <c r="E31" s="7" t="n"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Gate of Q3 (red cathode switch), R15 100k pull-down. PWM. HIGH = on.</t>
+          <t>Gate of Q4 (green cathode switch), R16 100k pull-down. PWM. HIGH = on. (Was LED_R before 16 Oct.)</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1310,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>LED_G</t>
+          <t>LED_B</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1322,7 +1321,7 @@
       <c r="E33" s="7" t="n"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Gate of Q4 (green cathode switch), R16 100k pull-down. PWM. HIGH = on.</t>
+          <t>Gate of Q5 (blue cathode switch), R17 100k pull-down. PWM. HIGH = on. (Was LED_G before 16 Oct.)</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2175,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2686,7 +2684,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>U1 P0.11 / P0.12 / P1.08 -&gt; Q3 / Q4 / Q5 gates (R15 / R16 / R17 100k to GND). Q3 / Q4 / Q5 drains -&gt; R8 1k / R9 560R / R10 560R -&gt; D2 R (4) / G (3) / B (2) cathodes</t>
+          <t>U1 P1.08 / P0.11 / P0.12 -&gt; Q3 / Q4 / Q5 gates (R15 / R16 / R17 100k to GND). Q3 / Q4 / Q5 drains -&gt; R8 1k / R9 560R / R10 560R -&gt; D2 R (4) / G (3) / B (2) cathodes</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
